--- a/04 - Channel Partner Scheme Code Generator.xlsx
+++ b/04 - Channel Partner Scheme Code Generator.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Desktop\vistex base file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IFB Process Automation\Vistex Project\Latest Doc\To Be\Off invoice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A0AC5E2-5A36-48EE-A06F-5EDAB48417F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578FD2C6-520A-415B-BBB7-A2DB3ACD6BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scheme Code Tool" sheetId="1" r:id="rId1"/>
-    <sheet name="Codebook" sheetId="3" r:id="rId2"/>
-    <sheet name="Sample Scenarios" sheetId="2" r:id="rId3"/>
+    <sheet name="MA Schem Code Tool" sheetId="5" r:id="rId1"/>
+    <sheet name="Sub Agreement Code Tool" sheetId="1" r:id="rId2"/>
+    <sheet name="Codebook" sheetId="3" r:id="rId3"/>
     <sheet name="Instructions" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sample Scenarios'!$A$4:$M$22</definedName>
     <definedName name="FinancialYears">Codebook!$J$2:$J$19</definedName>
     <definedName name="Months">Codebook!$H$2:$H$13</definedName>
     <definedName name="PeriodTypes">Codebook!$A$2:$A$6</definedName>
@@ -29,7 +28,6 @@
     <definedName name="StandardPeriods">Codebook!$B$2:$B$20</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -99,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="235">
   <si>
     <t>CHANNEL PARTNER INCENTIVE SCHEME CODE GENERATOR</t>
   </si>
@@ -219,222 +217,81 @@
     <t>2345678</t>
   </si>
   <si>
-    <t>SAMPLE SCENARIOS – CHANNEL PARTNER INCENTIVE SCHEME CODE</t>
-  </si>
-  <si>
-    <t>Examples cover standard FY periods, non-standard/custom periods, all 8 scheme types, both value/quantity bases, and repeat-sequence uniqueness.</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Standard Period</t>
-  </si>
-  <si>
-    <t>Custom Start</t>
-  </si>
-  <si>
-    <t>Custom End</t>
-  </si>
-  <si>
-    <t>Customer Code</t>
-  </si>
-  <si>
-    <t>Char Count</t>
-  </si>
-  <si>
-    <t>Monthly – Festive / Value</t>
-  </si>
-  <si>
     <t>M04</t>
   </si>
   <si>
-    <t>Monthly – Sellout / Quantity</t>
-  </si>
-  <si>
-    <t>Monthly – Liquidation / Value</t>
-  </si>
-  <si>
     <t>M01</t>
   </si>
   <si>
     <t>Liquidation</t>
   </si>
   <si>
-    <t>3456789</t>
-  </si>
-  <si>
-    <t>Quarterly – Tie up / Value</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>4567890</t>
-  </si>
-  <si>
-    <t>Quarterly – Festive / Quantity</t>
-  </si>
-  <si>
-    <t>5678901</t>
-  </si>
-  <si>
-    <t>Quarterly – Special / Value</t>
-  </si>
-  <si>
     <t>Q4</t>
   </si>
   <si>
     <t>Special Period</t>
   </si>
   <si>
-    <t>6789012</t>
-  </si>
-  <si>
-    <t>Half Yearly – Tie up / Quantity</t>
-  </si>
-  <si>
     <t>Half Yearly</t>
   </si>
   <si>
     <t>H1</t>
   </si>
   <si>
-    <t>7890123</t>
-  </si>
-  <si>
-    <t>Half Yearly – Sellout / Value</t>
-  </si>
-  <si>
     <t>H2</t>
   </si>
   <si>
-    <t>8901234</t>
-  </si>
-  <si>
-    <t>Annual – Tie up / Value</t>
-  </si>
-  <si>
     <t>Annual</t>
   </si>
   <si>
     <t>AN</t>
   </si>
   <si>
-    <t>9012345</t>
-  </si>
-  <si>
-    <t>Annual – Liquidation / Quantity</t>
-  </si>
-  <si>
-    <t>1122334</t>
-  </si>
-  <si>
-    <t>Custom – Sep-26 to Aug-27</t>
-  </si>
-  <si>
-    <t>Custom – Oct-26 to Mar-27</t>
-  </si>
-  <si>
     <t>Oct</t>
   </si>
   <si>
     <t>Mar</t>
   </si>
   <si>
-    <t>2234567</t>
-  </si>
-  <si>
-    <t>Custom – Dec-26 to Feb-27</t>
-  </si>
-  <si>
     <t>Dec</t>
   </si>
   <si>
     <t>Feb</t>
   </si>
   <si>
-    <t>3234567</t>
-  </si>
-  <si>
-    <t>Custom – Apr-26 to Sep-26</t>
-  </si>
-  <si>
     <t>Apr</t>
   </si>
   <si>
-    <t>4234567</t>
-  </si>
-  <si>
-    <t>Custom – Jan-27 to Jun-27</t>
-  </si>
-  <si>
     <t>Jan</t>
   </si>
   <si>
     <t>Jun</t>
   </si>
   <si>
-    <t>5234567</t>
-  </si>
-  <si>
-    <t>Repeat scheme – sequence 2</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Next FY – Monthly</t>
-  </si>
-  <si>
     <t>FY 2027-28</t>
   </si>
   <si>
-    <t>6234567</t>
-  </si>
-  <si>
-    <t>Next FY – Custom Sep-27 to Aug-28</t>
-  </si>
-  <si>
-    <t>7234567</t>
-  </si>
-  <si>
-    <t>Monthly – Cash Discount / Value</t>
-  </si>
-  <si>
     <t>M09</t>
   </si>
   <si>
     <t>Cash Discount</t>
   </si>
   <si>
-    <t>8234567</t>
-  </si>
-  <si>
-    <t>Quarterly – Growth / Value</t>
-  </si>
-  <si>
     <t>Q3</t>
   </si>
   <si>
     <t>Growth</t>
   </si>
   <si>
-    <t>9234567</t>
-  </si>
-  <si>
-    <t>Custom – FOC / Quantity Sep-Aug</t>
-  </si>
-  <si>
     <t>FOC</t>
   </si>
   <si>
-    <t>1334567</t>
-  </si>
-  <si>
-    <t>Custom-period interpretation: select the FY in which the scheme starts. Example FY 2026-27 + Sep to Aug = Sep-26 to Aug-27. If End Month is earlier than Start Month, the period crosses into the next calendar year.</t>
-  </si>
-  <si>
     <t>Standard Period Code</t>
   </si>
   <si>
@@ -849,19 +706,109 @@
     <t>PD</t>
   </si>
   <si>
-    <t>CC</t>
-  </si>
-  <si>
-    <t>CQ</t>
-  </si>
-  <si>
-    <t>Cluster of Customer</t>
-  </si>
-  <si>
-    <t>Cluster of Customer-SCALE</t>
-  </si>
-  <si>
     <t>1000675</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>Turnover Rebate-% Based (Amount Scale)-Festive</t>
+  </si>
+  <si>
+    <t>Turnover Rebate-% Based (Amount Scale)-Specific</t>
+  </si>
+  <si>
+    <t>Turnover Rebate-% Based (Amount Scale)-Period</t>
+  </si>
+  <si>
+    <t>Turnover Rebate - % Based (amount Scale) - Liquidation</t>
+  </si>
+  <si>
+    <t>CS</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>Quantity Rebate-$/unit (Qty Scale)-Festive</t>
+  </si>
+  <si>
+    <t>Quantity Rebate-$/unit (Qty Scale)-Specific</t>
+  </si>
+  <si>
+    <t>Quantity Rebate-$/unit (Qty Scale)-Annual</t>
+  </si>
+  <si>
+    <t>Quantity Rebate-$/unit (Qty Scale)-Liquidation</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-SCALE % Based (Amount Scale)-Festive</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-SCALE-% Based (Amount Scale)-Specific</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-SCALE-% Based (amount Scale) - Liquidation</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-$/unit (Qty Scale)-Festive</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-$/unit (Qty Scale)-Specific</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-$/unit (Qty Scale)-Liquidation</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-$/unit (Qty Scale)-Periodic</t>
+  </si>
+  <si>
+    <t>Cluster of Customer-SCALE-% Based (Amount Scale)-Periodic</t>
+  </si>
+  <si>
+    <t>KF</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>KP</t>
+  </si>
+  <si>
+    <t>KL</t>
+  </si>
+  <si>
+    <t>Party name</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Customer code</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Master Agreement</t>
+  </si>
+  <si>
+    <t>Final Master Agreement code</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>EP Electronics</t>
   </si>
 </sst>
 </file>
@@ -871,7 +818,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -884,78 +831,78 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFC65911"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF7F6000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -970,7 +917,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1019,12 +966,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF17365D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF2F8"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1046,11 +989,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1058,7 +1007,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1096,22 +1045,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1121,23 +1068,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1148,8 +1079,8 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1188,11 +1119,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SchemeCodeTable" displayName="SchemeCodeTable" ref="A6:P107">
-  <autoFilter ref="A6:P107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SchemeCodeTable" displayName="SchemeCodeTable" ref="A6:Q107">
+  <autoFilter ref="A6:Q107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Sr No"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Year Code_x000a_(YY)"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Financial Year"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Period Type"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Standard_x000a_Period"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Custom Start_x000a_Month"/>
@@ -1204,11 +1135,14 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Period Code">
       <calculatedColumnFormula>IF(C7="Custom Period",IF(OR(E7="",F7=""),"",""&amp;TEXT(MATCH(E7,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F7,Codebook!$H$2:$H$13,0),"00")),D7)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Type_x000a_Code"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Type_x000a_Code">
+      <calculatedColumnFormula>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G7,Codebook!$C$2:$C$50,0)),"")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Basis_x000a_Code"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Final SAP Scheme Code"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Char_x000a_Count"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Status"/>
+    <tableColumn id="17" xr3:uid="{0CB9E900-959D-41FA-997A-2B6A5FD2A1EA}" name="Party name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1498,12 +1432,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A218A6FF-FAEE-4815-8F50-E1CBE3C98EB8}">
+  <dimension ref="A2:G3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="17">
+        <v>1000589</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="17">
+        <v>27</v>
+      </c>
+      <c r="F3" s="17" t="str">
+        <f>_xlfn.CONCAT(A3,B3,C3,D3,E3)</f>
+        <v>MA-1000589-27</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>234</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F4E78"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P107"/>
+  <dimension ref="A1:Q107"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1519,10 +1515,11 @@
     <col min="14" max="14" width="28" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:17" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1541,8 +1538,8 @@
       <c r="O1" s="20"/>
       <c r="P1" s="20"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="23" t="s">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="20"/>
@@ -1561,8 +1558,8 @@
       <c r="O2" s="20"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="20"/>
@@ -1581,8 +1578,8 @@
       <c r="O3" s="20"/>
       <c r="P3" s="20"/>
     </row>
-    <row r="4" spans="1:16" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
+    <row r="4" spans="1:17" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="20"/>
@@ -1601,7 +1598,7 @@
       <c r="O4" s="20"/>
       <c r="P4" s="20"/>
     </row>
-    <row r="6" spans="1:16" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1650,8 +1647,11 @@
       <c r="P6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>C0908</v>
       </c>
       <c r="L7" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G7,Codebook!$C$2:$C$20,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G7,Codebook!$C$2:$C$50,0)),"")</f>
         <v>FS</v>
       </c>
       <c r="M7" s="6" t="str">
@@ -1705,7 +1705,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -1716,12 +1716,12 @@
         <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>31</v>
@@ -1729,16 +1729,16 @@
       <c r="I8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="29" t="s">
-        <v>251</v>
+      <c r="J8" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="K8" s="6" t="str">
         <f>IF(C8="Custom Period",IF(OR(E8="C",F8="C"),"C","C"&amp;TEXT(MATCH(E8,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F8,Codebook!$H$2:$H$13,0),"00")),D8)</f>
         <v>M01</v>
       </c>
       <c r="L8" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G8,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>TU</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G8,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M8" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H8,Codebook!$E$2:$E$3,0)),"")</f>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="N8" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>27M01-TUQ1-1000675</v>
+        <v>27M01-FSQ1-1000675</v>
       </c>
       <c r="O8" s="6">
         <f t="shared" si="1"/>
@@ -1757,7 +1757,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -1773,7 +1773,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>25</v>
@@ -1781,16 +1781,16 @@
       <c r="I9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="29" t="s">
-        <v>251</v>
+      <c r="J9" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="K9" s="6" t="str">
         <f>IF(C9="Custom Period",IF(OR(E9="C",F9="C"),"C","C"&amp;TEXT(MATCH(E9,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F9,Codebook!$H$2:$H$13,0),"00")),D9)</f>
         <v>Q2</v>
       </c>
       <c r="L9" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G9,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>LQ</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G9,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M9" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H9,Codebook!$E$2:$E$3,0)),"")</f>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N9" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>27Q2-LQV1-1000675</v>
+        <v>27Q2-FSV1-1000675</v>
       </c>
       <c r="O9" s="6">
         <f t="shared" si="1"/>
@@ -1809,7 +1809,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>4</v>
       </c>
@@ -1817,15 +1817,15 @@
         <v>20</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>31</v>
@@ -1833,16 +1833,16 @@
       <c r="I10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="29" t="s">
-        <v>230</v>
+      <c r="J10" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="K10" s="6" t="str">
         <f>IF(C10="Custom Period",IF(OR(E10="C",F10="C"),"C","C"&amp;TEXT(MATCH(E10,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F10,Codebook!$H$2:$H$13,0),"00")),D10)</f>
         <v>AN</v>
       </c>
       <c r="L10" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G10,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G10,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M10" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H10,Codebook!$E$2:$E$3,0)),"")</f>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="N10" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>27AN-PFQ1-1000177</v>
+        <v>27AN-FSQ1-1000177</v>
       </c>
       <c r="O10" s="6">
         <f t="shared" si="1"/>
@@ -1861,7 +1861,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>5</v>
       </c>
@@ -1873,13 +1873,13 @@
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>31</v>
@@ -1895,8 +1895,8 @@
         <v>C0507</v>
       </c>
       <c r="L11" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G11,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G11,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M11" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H11,Codebook!$E$2:$E$3,0)),"")</f>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="N11" s="7" t="str">
         <f t="shared" ref="N11" si="3">IF(OR(B11="",K11="",L11="",M11="",I11="",J11=""),"",RIGHT(B11,2)&amp;K11&amp;"-"&amp;L11&amp;M11&amp;I11&amp;"-"&amp;J11)</f>
-        <v>27C0507-PFQ1-2345678</v>
+        <v>27C0507-FSQ1-2345678</v>
       </c>
       <c r="O11" s="6">
         <f t="shared" ref="O11" si="4">IF(N11="","",LEN(N11))</f>
@@ -1915,7 +1915,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>5</v>
       </c>
@@ -1926,12 +1926,12 @@
         <v>33</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>25</v>
@@ -1939,16 +1939,16 @@
       <c r="I12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="29" t="s">
-        <v>230</v>
+      <c r="J12" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="K12" s="6" t="str">
         <f>IF(C12="Custom Period",IF(OR(E12="C",F12="C"),"C","C"&amp;TEXT(MATCH(E12,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F12,Codebook!$H$2:$H$13,0),"00")),D12)</f>
         <v>M07</v>
       </c>
       <c r="L12" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G12,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G12,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M12" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H12,Codebook!$E$2:$E$3,0)),"")</f>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="N12" s="7" t="str">
         <f t="shared" ref="N12" si="6">IF(OR(B12="",K12="",L12="",M12="",I12="",J12=""),"",RIGHT(B12,2)&amp;K12&amp;"-"&amp;L12&amp;M12&amp;I12&amp;"-"&amp;J12)</f>
-        <v>27M07-PFV1-1000177</v>
+        <v>27M07-FSV1-1000177</v>
       </c>
       <c r="O12" s="6">
         <f t="shared" ref="O12" si="7">IF(N12="","",LEN(N12))</f>
@@ -1967,7 +1967,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>5</v>
       </c>
@@ -1978,29 +1978,29 @@
         <v>28</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>230</v>
+        <v>55</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="K13" s="6" t="str">
         <f>IF(C13="Custom Period",IF(OR(E13="C",F13="C"),"C","C"&amp;TEXT(MATCH(E13,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F13,Codebook!$H$2:$H$13,0),"00")),D13)</f>
         <v>Q3</v>
       </c>
       <c r="L13" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G13,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G13,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M13" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H13,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="N13" s="7" t="str">
         <f t="shared" ref="N13" si="9">IF(OR(B13="",K13="",L13="",M13="",I13="",J13=""),"",RIGHT(B13,2)&amp;K13&amp;"-"&amp;L13&amp;M13&amp;I13&amp;"-"&amp;J13)</f>
-        <v>27Q3-PFV2-1000177</v>
+        <v>27Q3-FSV2-1000177</v>
       </c>
       <c r="O13" s="6">
         <f t="shared" ref="O13" si="10">IF(N13="","",LEN(N13))</f>
@@ -2019,7 +2019,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>5</v>
       </c>
@@ -2027,15 +2027,15 @@
         <v>20</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>31</v>
@@ -2043,16 +2043,16 @@
       <c r="I14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="29" t="s">
-        <v>251</v>
+      <c r="J14" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="K14" s="6" t="str">
         <f>IF(C14="Custom Period",IF(OR(E14="C",F14="C"),"C","C"&amp;TEXT(MATCH(E14,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F14,Codebook!$H$2:$H$13,0),"00")),D14)</f>
         <v>H1</v>
       </c>
       <c r="L14" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G14,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G14,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M14" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H14,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="N14" s="7" t="str">
         <f t="shared" ref="N14" si="12">IF(OR(B14="",K14="",L14="",M14="",I14="",J14=""),"",RIGHT(B14,2)&amp;K14&amp;"-"&amp;L14&amp;M14&amp;I14&amp;"-"&amp;J14)</f>
-        <v>27H1-PFQ1-1000675</v>
+        <v>27H1-FSQ1-1000675</v>
       </c>
       <c r="O14" s="6">
         <f t="shared" ref="O14" si="13">IF(N14="","",LEN(N14))</f>
@@ -2071,7 +2071,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>5</v>
       </c>
@@ -2079,15 +2079,15 @@
         <v>20</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>25</v>
@@ -2095,16 +2095,16 @@
       <c r="I15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="29" t="s">
-        <v>230</v>
+      <c r="J15" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="K15" s="6" t="str">
         <f>IF(C15="Custom Period",IF(OR(E15="C",F15="C"),"C","C"&amp;TEXT(MATCH(E15,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F15,Codebook!$H$2:$H$13,0),"00")),D15)</f>
         <v>AN</v>
       </c>
       <c r="L15" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G15,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G15,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M15" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H15,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="N15" s="7" t="str">
         <f t="shared" ref="N15" si="15">IF(OR(B15="",K15="",L15="",M15="",I15="",J15=""),"",RIGHT(B15,2)&amp;K15&amp;"-"&amp;L15&amp;M15&amp;I15&amp;"-"&amp;J15)</f>
-        <v>27AN-PFV1-1000177</v>
+        <v>27AN-FSV1-1000177</v>
       </c>
       <c r="O15" s="6">
         <f t="shared" ref="O15" si="16">IF(N15="","",LEN(N15))</f>
@@ -2123,7 +2123,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>5</v>
       </c>
@@ -2135,13 +2135,13 @@
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>25</v>
@@ -2157,8 +2157,8 @@
         <v>C1112</v>
       </c>
       <c r="L16" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G16,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G16,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M16" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H16,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="N16" s="7" t="str">
         <f t="shared" ref="N16" si="18">IF(OR(B16="",K16="",L16="",M16="",I16="",J16=""),"",RIGHT(B16,2)&amp;K16&amp;"-"&amp;L16&amp;M16&amp;I16&amp;"-"&amp;J16)</f>
-        <v>27C1112-PFV1-2345678</v>
+        <v>27C1112-FSV1-2345678</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" ref="O16" si="19">IF(N16="","",LEN(N16))</f>
@@ -2195,7 +2195,7 @@
         <v>23</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>31</v>
@@ -2203,16 +2203,16 @@
       <c r="I17" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="29" t="s">
-        <v>230</v>
+      <c r="J17" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="K17" s="6" t="str">
         <f>IF(C17="Custom Period",IF(OR(E17="C",F17="C"),"C","C"&amp;TEXT(MATCH(E17,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F17,Codebook!$H$2:$H$13,0),"00")),D17)</f>
         <v>C0908</v>
       </c>
       <c r="L17" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G17,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G17,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M17" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H17,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="N17" s="7" t="str">
         <f t="shared" ref="N17" si="21">IF(OR(B17="",K17="",L17="",M17="",I17="",J17=""),"",RIGHT(B17,2)&amp;K17&amp;"-"&amp;L17&amp;M17&amp;I17&amp;"-"&amp;J17)</f>
-        <v>27C0908-PFQ1-1000177</v>
+        <v>27C0908-FSQ1-1000177</v>
       </c>
       <c r="O17" s="6">
         <f t="shared" ref="O17" si="22">IF(N17="","",LEN(N17))</f>
@@ -2251,7 +2251,7 @@
         <v>23</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>25</v>
@@ -2259,16 +2259,16 @@
       <c r="I18" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J18" s="29" t="s">
-        <v>251</v>
+      <c r="J18" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="K18" s="6" t="str">
         <f>IF(C18="Custom Period",IF(OR(E18="C",F18="C"),"C","C"&amp;TEXT(MATCH(E18,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F18,Codebook!$H$2:$H$13,0),"00")),D18)</f>
         <v>Q2</v>
       </c>
       <c r="L18" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$20,MATCH(G18,Codebook!$C$2:$C$20,0)),"")</f>
-        <v>PF</v>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G18,Codebook!$C$2:$C$50,0)),"")</f>
+        <v>FS</v>
       </c>
       <c r="M18" s="6" t="str">
         <f>IFERROR(INDEX(Codebook!$F$2:$F$3,MATCH(H18,Codebook!$E$2:$E$3,0)),"")</f>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="N18" s="7" t="str">
         <f t="shared" ref="N18" si="24">IF(OR(B18="",K18="",L18="",M18="",I18="",J18=""),"",RIGHT(B18,2)&amp;K18&amp;"-"&amp;L18&amp;M18&amp;I18&amp;"-"&amp;J18)</f>
-        <v>27Q2-PFV1-1000675</v>
+        <v>27Q2-FSV1-1000675</v>
       </c>
       <c r="O18" s="6">
         <f t="shared" ref="O18" si="25">IF(N18="","",LEN(N18))</f>
@@ -2291,21 +2291,27 @@
       <c r="A19" s="2">
         <v>12</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
+      <c r="B19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
       <c r="J19" s="5"/>
-      <c r="K19" s="6">
+      <c r="K19" s="6" t="str">
         <f>IF(C19="Custom Period",IF(OR(E19="C",F19="C"),"C","C"&amp;TEXT(MATCH(E19,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F19,Codebook!$H$2:$H$13,0),"00")),D19)</f>
-        <v>0</v>
+        <v>Q3</v>
       </c>
       <c r="L19" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G19,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G19,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M19" s="6" t="str">
@@ -2322,7 +2328,7 @@
       </c>
       <c r="P19" s="6" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CHECK INPUT</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -2343,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G20,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G20,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M20" s="6" t="str">
@@ -2381,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G21,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G21,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M21" s="6" t="str">
@@ -2419,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G22,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G22,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M22" s="6" t="str">
@@ -2457,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G23,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G23,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M23" s="6" t="str">
@@ -2495,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G24,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G24,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M24" s="6" t="str">
@@ -2533,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G25,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G25,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M25" s="6" t="str">
@@ -2571,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G26,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G26,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M26" s="6" t="str">
@@ -2609,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G27,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G27,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M27" s="6" t="str">
@@ -2647,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G28,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G28,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M28" s="6" t="str">
@@ -2685,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G29,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G29,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M29" s="6" t="str">
@@ -2723,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G30,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G30,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M30" s="6" t="str">
@@ -2761,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G31,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G31,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M31" s="6" t="str">
@@ -2799,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G32,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G32,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M32" s="6" t="str">
@@ -2837,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G33,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G33,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M33" s="6" t="str">
@@ -2875,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G34,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G34,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M34" s="6" t="str">
@@ -2913,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G35,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G35,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M35" s="6" t="str">
@@ -2951,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G36,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G36,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M36" s="6" t="str">
@@ -2989,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G37,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G37,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M37" s="6" t="str">
@@ -3027,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="L38" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G38,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G38,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M38" s="6" t="str">
@@ -3065,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="L39" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G39,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G39,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M39" s="6" t="str">
@@ -3103,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L40" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G40,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G40,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M40" s="6" t="str">
@@ -3141,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G41,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G41,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M41" s="6" t="str">
@@ -3179,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G42,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G42,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M42" s="6" t="str">
@@ -3217,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G43,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G43,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M43" s="6" t="str">
@@ -3255,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G44,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G44,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M44" s="6" t="str">
@@ -3293,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G45,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G45,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M45" s="6" t="str">
@@ -3331,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G46,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G46,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M46" s="6" t="str">
@@ -3369,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G47,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G47,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M47" s="6" t="str">
@@ -3407,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G48,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G48,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M48" s="6" t="str">
@@ -3445,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G49,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G49,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M49" s="6" t="str">
@@ -3483,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G50,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G50,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M50" s="6" t="str">
@@ -3521,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G51,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G51,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M51" s="6" t="str">
@@ -3559,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G52,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G52,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M52" s="6" t="str">
@@ -3597,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G53,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G53,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M53" s="6" t="str">
@@ -3635,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="L54" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G54,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G54,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M54" s="6" t="str">
@@ -3673,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="L55" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G55,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G55,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M55" s="6" t="str">
@@ -3711,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="L56" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G56,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G56,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M56" s="6" t="str">
@@ -3749,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="L57" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G57,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G57,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M57" s="6" t="str">
@@ -3787,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="L58" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G58,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G58,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M58" s="6" t="str">
@@ -3825,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="L59" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G59,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G59,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M59" s="6" t="str">
@@ -3863,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="L60" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G60,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G60,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M60" s="6" t="str">
@@ -3901,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G61,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G61,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M61" s="6" t="str">
@@ -3939,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="L62" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G62,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G62,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M62" s="6" t="str">
@@ -3977,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G63,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G63,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M63" s="6" t="str">
@@ -4015,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="L64" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G64,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G64,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M64" s="6" t="str">
@@ -4053,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="L65" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G65,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G65,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M65" s="6" t="str">
@@ -4091,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G66,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G66,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M66" s="6" t="str">
@@ -4129,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="L67" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G67,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G67,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M67" s="6" t="str">
@@ -4167,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G68,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G68,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M68" s="6" t="str">
@@ -4205,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G69,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G69,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M69" s="6" t="str">
@@ -4243,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G70,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G70,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M70" s="6" t="str">
@@ -4281,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="L71" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G71,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G71,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M71" s="6" t="str">
@@ -4319,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G72,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G72,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M72" s="6" t="str">
@@ -4357,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G73,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G73,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M73" s="6" t="str">
@@ -4395,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="L74" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G74,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G74,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M74" s="6" t="str">
@@ -4433,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G75,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G75,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M75" s="6" t="str">
@@ -4471,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="L76" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G76,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G76,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M76" s="6" t="str">
@@ -4509,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="L77" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G77,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G77,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M77" s="6" t="str">
@@ -4547,7 +4553,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G78,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G78,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M78" s="6" t="str">
@@ -4585,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G79,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G79,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M79" s="6" t="str">
@@ -4623,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G80,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G80,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M80" s="6" t="str">
@@ -4661,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G81,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G81,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M81" s="6" t="str">
@@ -4699,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G82,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G82,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M82" s="6" t="str">
@@ -4737,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G83,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G83,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M83" s="6" t="str">
@@ -4775,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="L84" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G84,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G84,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M84" s="6" t="str">
@@ -4813,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="L85" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G85,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G85,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M85" s="6" t="str">
@@ -4851,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="L86" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G86,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G86,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M86" s="6" t="str">
@@ -4889,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G87,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G87,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M87" s="6" t="str">
@@ -4927,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="L88" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G88,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G88,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M88" s="6" t="str">
@@ -4965,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="L89" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G89,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G89,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M89" s="6" t="str">
@@ -5003,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="L90" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G90,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G90,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M90" s="6" t="str">
@@ -5041,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G91,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G91,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M91" s="6" t="str">
@@ -5079,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G92,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G92,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M92" s="6" t="str">
@@ -5117,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="L93" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G93,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G93,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M93" s="6" t="str">
@@ -5155,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G94,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G94,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M94" s="6" t="str">
@@ -5193,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="L95" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G95,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G95,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M95" s="6" t="str">
@@ -5231,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="L96" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G96,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G96,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
@@ -5269,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="L97" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G97,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G97,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
@@ -5307,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="L98" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G98,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G98,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M98" s="6" t="str">
@@ -5345,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="L99" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G99,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G99,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M99" s="6" t="str">
@@ -5383,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="L100" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G100,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G100,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M100" s="6" t="str">
@@ -5421,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="L101" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G101,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G101,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M101" s="6" t="str">
@@ -5459,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="L102" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G102,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G102,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M102" s="6" t="str">
@@ -5497,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="L103" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G103,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G103,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M103" s="6" t="str">
@@ -5535,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="L104" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G104,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G104,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M104" s="6" t="str">
@@ -5573,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G105,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G105,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M105" s="6" t="str">
@@ -5611,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G106,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G106,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M106" s="6" t="str">
@@ -5649,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="6" t="str">
-        <f>IFERROR(INDEX(Codebook!$D$2:$D$9,MATCH(G107,Codebook!$C$2:$C$9,0)),"")</f>
+        <f>IFERROR(INDEX(Codebook!$D$2:$D$50,MATCH(G107,Codebook!$C$2:$C$50,0)),"")</f>
         <v/>
       </c>
       <c r="M107" s="6" t="str">
@@ -5721,9 +5727,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Selection" error="Please select a value from the dropdown." promptTitle="Select from list" prompt="Select scheme type." xr:uid="{4C614A1D-D758-4245-81F0-92A2E4D30516}">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Invalid Selection" error="Please select a value from the dropdown." promptTitle="Select from list" prompt="Select scheme type." xr:uid="{9128E93E-C33A-43E3-8462-D87A827D4216}">
           <x14:formula1>
-            <xm:f>Codebook!$C$2:$C$19</xm:f>
+            <xm:f>Codebook!$C$2:$C$30</xm:f>
           </x14:formula1>
           <xm:sqref>G7:G107</xm:sqref>
         </x14:dataValidation>
@@ -5733,7 +5739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFA5A5A5"/>
@@ -5743,7 +5749,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="59.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5752,25 +5758,25 @@
         <v>6</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>5</v>
@@ -5781,28 +5787,28 @@
         <v>33</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="J2" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -5810,71 +5816,71 @@
         <v>28</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="H4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
         <v>77</v>
-      </c>
-      <c r="J4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
@@ -5885,1339 +5891,420 @@
         <v>21</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B7" s="9" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="J7" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="J8" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="9" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>239</v>
+        <v>57</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>192</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="J10" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B11" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>240</v>
+      <c r="C11" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>193</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>146</v>
+        <v>99</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="J11" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>244</v>
+        <v>101</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>197</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>150</v>
+        <v>103</v>
       </c>
       <c r="J12" t="s">
-        <v>151</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B13" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>242</v>
+        <v>105</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>195</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>153</v>
+        <v>106</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>241</v>
+        <v>40</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>194</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="J14" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>246</v>
+      <c r="C15" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>199</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="J15" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>245</v>
+        <v>59</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>198</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>243</v>
+        <v>41</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="J17" t="s">
-        <v>162</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>249</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>247</v>
+        <v>44</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>202</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="J18" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>248</v>
+        <v>45</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>203</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="J19" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="9" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>204</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C21" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>205</v>
+      </c>
       <c r="G21" s="9" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C22" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>209</v>
+      </c>
       <c r="G22" s="9" t="s">
-        <v>169</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C23" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>210</v>
+      </c>
       <c r="G23" s="9" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C24" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>211</v>
+      </c>
       <c r="G24" s="9" t="s">
-        <v>171</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C25" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>212</v>
+      </c>
       <c r="G25" s="9" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G26" s="9" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G27" s="9" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G28" s="9" t="s">
-        <v>174</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G29" s="9" t="s">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G30" s="9" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G31" s="9" t="s">
-        <v>177</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="G32" s="9" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G33" s="9" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G34" s="9" t="s">
-        <v>179</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G35" s="9" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="7:7" x14ac:dyDescent="0.35">
       <c r="G36" s="9" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D2:D25">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-    </row>
-    <row r="2" spans="1:13" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-    </row>
-    <row r="4" spans="1:13" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="18" t="str">
-        <f>IF(C5="Custom Period","C"&amp;TEXT(MATCH(E5,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F5,Codebook!$H$2:$H$13,0),"00"),D5)</f>
-        <v>M04</v>
-      </c>
-      <c r="L5" s="18" t="str">
-        <f>RIGHT(B5,2)&amp;K5&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G5,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H5,Codebook!$E$2:$E$3,0))&amp;I5&amp;"-"&amp;J5</f>
-        <v>27M04-FSV1-1234567</v>
-      </c>
-      <c r="M5" s="18">
-        <f t="shared" ref="M5:M25" si="0">LEN(L5)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="18" t="str">
-        <f>IF(C6="Custom Period","C"&amp;TEXT(MATCH(E6,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F6,Codebook!$H$2:$H$13,0),"00"),D6)</f>
-        <v>M10</v>
-      </c>
-      <c r="L6" s="18" t="str">
-        <f>RIGHT(B6,2)&amp;K6&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G6,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H6,Codebook!$E$2:$E$3,0))&amp;I6&amp;"-"&amp;J6</f>
-        <v>27M10-SOQ1-2345678</v>
-      </c>
-      <c r="M6" s="18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="18" t="str">
-        <f>IF(C7="Custom Period","C"&amp;TEXT(MATCH(E7,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F7,Codebook!$H$2:$H$13,0),"00"),D7)</f>
-        <v>M01</v>
-      </c>
-      <c r="L7" s="18" t="str">
-        <f>RIGHT(B7,2)&amp;K7&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G7,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H7,Codebook!$E$2:$E$3,0))&amp;I7&amp;"-"&amp;J7</f>
-        <v>27M01-LQV1-3456789</v>
-      </c>
-      <c r="M7" s="18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="18" t="str">
-        <f>IF(C8="Custom Period","C"&amp;TEXT(MATCH(E8,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F8,Codebook!$H$2:$H$13,0),"00"),D8)</f>
-        <v>Q1</v>
-      </c>
-      <c r="L8" s="18" t="str">
-        <f>RIGHT(B8,2)&amp;K8&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G8,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H8,Codebook!$E$2:$E$3,0))&amp;I8&amp;"-"&amp;J8</f>
-        <v>27Q1-TUV1-4567890</v>
-      </c>
-      <c r="M8" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="18" t="str">
-        <f>IF(C9="Custom Period","C"&amp;TEXT(MATCH(E9,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F9,Codebook!$H$2:$H$13,0),"00"),D9)</f>
-        <v>Q2</v>
-      </c>
-      <c r="L9" s="18" t="str">
-        <f>RIGHT(B9,2)&amp;K9&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G9,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H9,Codebook!$E$2:$E$3,0))&amp;I9&amp;"-"&amp;J9</f>
-        <v>27Q2-FSQ1-5678901</v>
-      </c>
-      <c r="M9" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" s="18" t="str">
-        <f>IF(C10="Custom Period","C"&amp;TEXT(MATCH(E10,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F10,Codebook!$H$2:$H$13,0),"00"),D10)</f>
-        <v>Q4</v>
-      </c>
-      <c r="L10" s="18" t="str">
-        <f>RIGHT(B10,2)&amp;K10&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G10,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H10,Codebook!$E$2:$E$3,0))&amp;I10&amp;"-"&amp;J10</f>
-        <v>27Q4-SPV1-6789012</v>
-      </c>
-      <c r="M10" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" s="18" t="str">
-        <f>IF(C11="Custom Period","C"&amp;TEXT(MATCH(E11,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F11,Codebook!$H$2:$H$13,0),"00"),D11)</f>
-        <v>H1</v>
-      </c>
-      <c r="L11" s="18" t="str">
-        <f>RIGHT(B11,2)&amp;K11&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G11,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H11,Codebook!$E$2:$E$3,0))&amp;I11&amp;"-"&amp;J11</f>
-        <v>27H1-TUQ1-7890123</v>
-      </c>
-      <c r="M11" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="18" t="str">
-        <f>IF(C12="Custom Period","C"&amp;TEXT(MATCH(E12,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F12,Codebook!$H$2:$H$13,0),"00"),D12)</f>
-        <v>H2</v>
-      </c>
-      <c r="L12" s="18" t="str">
-        <f>RIGHT(B12,2)&amp;K12&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G12,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H12,Codebook!$E$2:$E$3,0))&amp;I12&amp;"-"&amp;J12</f>
-        <v>27H2-SOV1-8901234</v>
-      </c>
-      <c r="M12" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="K13" s="18" t="str">
-        <f>IF(C13="Custom Period","C"&amp;TEXT(MATCH(E13,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F13,Codebook!$H$2:$H$13,0),"00"),D13)</f>
-        <v>AN</v>
-      </c>
-      <c r="L13" s="18" t="str">
-        <f>RIGHT(B13,2)&amp;K13&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G13,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H13,Codebook!$E$2:$E$3,0))&amp;I13&amp;"-"&amp;J13</f>
-        <v>27AN-TUV1-9012345</v>
-      </c>
-      <c r="M13" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="K14" s="18" t="str">
-        <f>IF(C14="Custom Period","C"&amp;TEXT(MATCH(E14,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F14,Codebook!$H$2:$H$13,0),"00"),D14)</f>
-        <v>AN</v>
-      </c>
-      <c r="L14" s="18" t="str">
-        <f>RIGHT(B14,2)&amp;K14&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G14,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H14,Codebook!$E$2:$E$3,0))&amp;I14&amp;"-"&amp;J14</f>
-        <v>27AN-LQQ1-1122334</v>
-      </c>
-      <c r="M14" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K15" s="18" t="str">
-        <f>IF(C15="Custom Period","C"&amp;TEXT(MATCH(E15,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F15,Codebook!$H$2:$H$13,0),"00"),D15)</f>
-        <v>C0908</v>
-      </c>
-      <c r="L15" s="18" t="str">
-        <f>RIGHT(B15,2)&amp;K15&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G15,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H15,Codebook!$E$2:$E$3,0))&amp;I15&amp;"-"&amp;J15</f>
-        <v>27C0908-TUV1-1234567</v>
-      </c>
-      <c r="M15" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" s="18" t="str">
-        <f>IF(C16="Custom Period","C"&amp;TEXT(MATCH(E16,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F16,Codebook!$H$2:$H$13,0),"00"),D16)</f>
-        <v>C1003</v>
-      </c>
-      <c r="L16" s="18" t="str">
-        <f>RIGHT(B16,2)&amp;K16&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G16,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H16,Codebook!$E$2:$E$3,0))&amp;I16&amp;"-"&amp;J16</f>
-        <v>27C1003-SPQ1-2234567</v>
-      </c>
-      <c r="M16" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="K17" s="18" t="str">
-        <f>IF(C17="Custom Period","C"&amp;TEXT(MATCH(E17,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F17,Codebook!$H$2:$H$13,0),"00"),D17)</f>
-        <v>C1202</v>
-      </c>
-      <c r="L17" s="18" t="str">
-        <f>RIGHT(B17,2)&amp;K17&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G17,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H17,Codebook!$E$2:$E$3,0))&amp;I17&amp;"-"&amp;J17</f>
-        <v>27C1202-FSV1-3234567</v>
-      </c>
-      <c r="M17" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" s="18" t="str">
-        <f>IF(C18="Custom Period","C"&amp;TEXT(MATCH(E18,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F18,Codebook!$H$2:$H$13,0),"00"),D18)</f>
-        <v>C0409</v>
-      </c>
-      <c r="L18" s="18" t="str">
-        <f>RIGHT(B18,2)&amp;K18&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G18,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H18,Codebook!$E$2:$E$3,0))&amp;I18&amp;"-"&amp;J18</f>
-        <v>27C0409-SOQ1-4234567</v>
-      </c>
-      <c r="M18" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="K19" s="18" t="str">
-        <f>IF(C19="Custom Period","C"&amp;TEXT(MATCH(E19,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F19,Codebook!$H$2:$H$13,0),"00"),D19)</f>
-        <v>C0106</v>
-      </c>
-      <c r="L19" s="18" t="str">
-        <f>RIGHT(B19,2)&amp;K19&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G19,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H19,Codebook!$E$2:$E$3,0))&amp;I19&amp;"-"&amp;J19</f>
-        <v>27C0106-LQV1-5234567</v>
-      </c>
-      <c r="M19" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="K20" s="18" t="str">
-        <f>IF(C20="Custom Period","C"&amp;TEXT(MATCH(E20,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F20,Codebook!$H$2:$H$13,0),"00"),D20)</f>
-        <v>C0908</v>
-      </c>
-      <c r="L20" s="18" t="str">
-        <f>RIGHT(B20,2)&amp;K20&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G20,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H20,Codebook!$E$2:$E$3,0))&amp;I20&amp;"-"&amp;J20</f>
-        <v>27C0908-TUV2-1234567</v>
-      </c>
-      <c r="M20" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" s="18" t="str">
-        <f>IF(C21="Custom Period","C"&amp;TEXT(MATCH(E21,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F21,Codebook!$H$2:$H$13,0),"00"),D21)</f>
-        <v>M04</v>
-      </c>
-      <c r="L21" s="18" t="str">
-        <f>RIGHT(B21,2)&amp;K21&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G21,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H21,Codebook!$E$2:$E$3,0))&amp;I21&amp;"-"&amp;J21</f>
-        <v>28M04-FSV1-6234567</v>
-      </c>
-      <c r="M21" s="18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="18" t="str">
-        <f>IF(C22="Custom Period","C"&amp;TEXT(MATCH(E22,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F22,Codebook!$H$2:$H$13,0),"00"),D22)</f>
-        <v>C0908</v>
-      </c>
-      <c r="L22" s="18" t="str">
-        <f>RIGHT(B22,2)&amp;K22&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G22,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H22,Codebook!$E$2:$E$3,0))&amp;I22&amp;"-"&amp;J22</f>
-        <v>28C0908-TUQ1-7234567</v>
-      </c>
-      <c r="M22" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="K23" s="18" t="str">
-        <f>IF(C23="Custom Period","C"&amp;TEXT(MATCH(E23,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F23,Codebook!$H$2:$H$13,0),"00"),D23)</f>
-        <v>M09</v>
-      </c>
-      <c r="L23" s="18" t="str">
-        <f>RIGHT(B23,2)&amp;K23&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G23,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H23,Codebook!$E$2:$E$3,0))&amp;I23&amp;"-"&amp;J23</f>
-        <v>27M09-CDV1-8234567</v>
-      </c>
-      <c r="M23" s="18">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I24" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="K24" s="18" t="str">
-        <f>IF(C24="Custom Period","C"&amp;TEXT(MATCH(E24,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F24,Codebook!$H$2:$H$13,0),"00"),D24)</f>
-        <v>Q3</v>
-      </c>
-      <c r="L24" s="18" t="str">
-        <f>RIGHT(B24,2)&amp;K24&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G24,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H24,Codebook!$E$2:$E$3,0))&amp;I24&amp;"-"&amp;J24</f>
-        <v>27Q3-GRV1-9234567</v>
-      </c>
-      <c r="M24" s="18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" s="18" t="str">
-        <f>IF(C25="Custom Period","C"&amp;TEXT(MATCH(E25,Codebook!$H$2:$H$13,0),"00")&amp;TEXT(MATCH(F25,Codebook!$H$2:$H$13,0),"00"),D25)</f>
-        <v>C0908</v>
-      </c>
-      <c r="L25" s="18" t="str">
-        <f>RIGHT(B25,2)&amp;K25&amp;"-"&amp;INDEX(Codebook!$D$2:$D$9,MATCH(G25,Codebook!$C$2:$C$9,0))&amp;INDEX(Codebook!$F$2:$F$3,MATCH(H25,Codebook!$E$2:$E$3,0))&amp;I25&amp;"-"&amp;J25</f>
-        <v>27C0908-FCQ1-1334567</v>
-      </c>
-      <c r="M25" s="18">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A28" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:M22" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
-  <mergeCells count="3">
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A28:M28"/>
-  </mergeCells>
-  <conditionalFormatting sqref="M5:M22">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>M5&gt;20</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -7236,8 +6323,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="27" t="s">
-        <v>182</v>
+      <c r="A1" s="19" t="s">
+        <v>135</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -7247,87 +6334,87 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>188</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>189</v>
+        <v>142</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>190</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>192</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>194</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>195</v>
+        <v>148</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="28" t="s">
-        <v>203</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="21" t="s">
+        <v>156</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -7335,116 +6422,116 @@
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>36</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B24" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
